--- a/docs/oc-mensuales/suministro-de-combustibles/mar-2025.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/mar-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17820,7 +17820,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19101,7 +19101,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20016,7 +20016,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20077,7 +20077,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20626,7 +20626,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21175,7 +21175,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21602,7 +21602,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21663,7 +21663,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22273,7 +22273,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23005,7 +23005,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23188,7 +23188,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23249,7 +23249,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23310,7 +23310,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23554,7 +23554,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23615,7 +23615,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24042,7 +24042,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24103,7 +24103,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24652,7 +24652,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24713,7 +24713,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24957,7 +24957,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25689,7 +25689,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25933,7 +25933,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26055,7 +26055,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26238,7 +26238,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26299,7 +26299,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26360,7 +26360,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26421,7 +26421,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26909,7 +26909,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26970,7 +26970,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27275,7 +27275,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27458,7 +27458,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27519,7 +27519,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27641,7 +27641,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27702,7 +27702,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28617,7 +28617,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28739,7 +28739,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28861,7 +28861,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29227,7 +29227,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29471,7 +29471,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29593,7 +29593,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29837,7 +29837,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29959,7 +29959,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30081,7 +30081,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30142,7 +30142,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30203,7 +30203,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30569,7 +30569,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30813,7 +30813,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30874,7 +30874,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31179,7 +31179,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31240,7 +31240,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31301,7 +31301,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31362,7 +31362,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31423,7 +31423,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31484,7 +31484,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31606,7 +31606,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31728,7 +31728,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31789,7 +31789,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31911,7 +31911,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32033,7 +32033,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32155,7 +32155,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32399,7 +32399,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32521,7 +32521,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32643,7 +32643,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32765,7 +32765,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32826,7 +32826,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32887,7 +32887,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32948,7 +32948,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33131,7 +33131,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33192,7 +33192,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33253,7 +33253,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33314,7 +33314,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33497,7 +33497,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33558,7 +33558,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33741,7 +33741,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33802,7 +33802,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33863,7 +33863,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33924,7 +33924,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33985,7 +33985,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34168,7 +34168,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34229,7 +34229,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34290,7 +34290,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34351,7 +34351,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34412,7 +34412,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34473,7 +34473,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34717,7 +34717,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34839,7 +34839,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34900,7 +34900,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34961,7 +34961,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35083,7 +35083,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35144,7 +35144,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35266,7 +35266,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35388,7 +35388,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35449,7 +35449,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35510,7 +35510,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35693,7 +35693,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35815,7 +35815,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35876,7 +35876,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36059,7 +36059,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36120,7 +36120,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36181,7 +36181,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36242,7 +36242,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36425,7 +36425,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36486,7 +36486,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36547,7 +36547,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36730,7 +36730,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36852,7 +36852,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36974,7 +36974,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37035,7 +37035,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37218,7 +37218,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37279,7 +37279,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37340,7 +37340,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37645,7 +37645,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37767,7 +37767,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37950,7 +37950,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38011,7 +38011,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38072,7 +38072,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38194,7 +38194,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38255,7 +38255,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38316,7 +38316,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38377,7 +38377,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38438,7 +38438,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38560,7 +38560,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38682,7 +38682,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38697,7 +38697,7 @@
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
@@ -38747,7 +38747,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38808,7 +38808,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38869,7 +38869,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38930,7 +38930,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39052,7 +39052,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39174,7 +39174,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39235,7 +39235,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39296,7 +39296,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39418,7 +39418,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39479,7 +39479,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39540,7 +39540,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39601,7 +39601,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39723,7 +39723,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39784,7 +39784,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39845,7 +39845,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39906,7 +39906,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39967,7 +39967,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40028,7 +40028,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40089,7 +40089,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40150,7 +40150,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40211,7 +40211,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40333,7 +40333,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40394,7 +40394,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40455,7 +40455,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40516,7 +40516,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40577,7 +40577,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40638,7 +40638,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40699,7 +40699,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40760,7 +40760,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40821,7 +40821,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40882,7 +40882,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40943,7 +40943,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41004,7 +41004,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41065,7 +41065,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41126,7 +41126,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41187,7 +41187,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41248,7 +41248,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41309,7 +41309,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41370,7 +41370,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41431,7 +41431,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41492,7 +41492,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41553,7 +41553,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41614,7 +41614,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41675,7 +41675,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41736,7 +41736,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41797,7 +41797,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41858,7 +41858,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41919,7 +41919,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41980,7 +41980,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42041,7 +42041,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42102,7 +42102,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42163,7 +42163,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42224,7 +42224,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42346,7 +42346,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42407,7 +42407,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42468,7 +42468,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42529,7 +42529,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42590,7 +42590,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42651,7 +42651,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42712,7 +42712,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42773,7 +42773,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -42895,7 +42895,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43017,7 +43017,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43078,7 +43078,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43139,7 +43139,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43200,7 +43200,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43261,7 +43261,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43322,7 +43322,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43383,7 +43383,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43444,7 +43444,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43505,7 +43505,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43566,7 +43566,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43627,7 +43627,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43688,7 +43688,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43749,7 +43749,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43810,7 +43810,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -43825,7 +43825,7 @@
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
@@ -43875,7 +43875,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -43936,7 +43936,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -43997,7 +43997,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44058,7 +44058,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44119,7 +44119,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44241,7 +44241,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44302,7 +44302,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44363,7 +44363,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -44424,7 +44424,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -44485,7 +44485,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44546,7 +44546,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -44607,7 +44607,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -44668,7 +44668,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44729,7 +44729,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -44790,7 +44790,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -44851,7 +44851,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -44912,7 +44912,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -44973,7 +44973,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45034,7 +45034,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45095,7 +45095,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45156,7 +45156,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45217,7 +45217,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45232,7 +45232,7 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
@@ -45282,7 +45282,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45343,7 +45343,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45404,7 +45404,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45465,7 +45465,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45526,7 +45526,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -45648,7 +45648,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45663,7 +45663,7 @@
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
@@ -45713,7 +45713,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45774,7 +45774,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45835,7 +45835,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -45896,7 +45896,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -45957,7 +45957,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -46018,7 +46018,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46079,7 +46079,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46140,7 +46140,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46201,7 +46201,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46262,7 +46262,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46323,7 +46323,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46384,7 +46384,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46445,7 +46445,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -46506,7 +46506,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46567,7 +46567,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -46689,7 +46689,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -46750,7 +46750,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -46811,7 +46811,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -46872,7 +46872,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -46933,7 +46933,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -46994,7 +46994,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47116,7 +47116,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -47177,7 +47177,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -47192,7 +47192,7 @@
       </c>
       <c r="K766" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L766" t="inlineStr">
@@ -47242,7 +47242,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -47303,7 +47303,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47364,7 +47364,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -47425,7 +47425,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -47486,7 +47486,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -47547,7 +47547,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -47608,7 +47608,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -47669,7 +47669,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -47730,7 +47730,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -47791,7 +47791,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -47852,7 +47852,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -47913,7 +47913,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -47974,7 +47974,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -48035,7 +48035,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
